--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,2134 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/60271280</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136545658</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105365</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1898</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klådris</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Myricaria germanica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Desv.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514454</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7010754</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136545658</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136543593</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>515160</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7010569</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136543593</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136547430</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514727</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7010648</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547430</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136550510</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43280</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>515231</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7010555</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136550510</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136541918</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43495</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>515230</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7010554</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136541918</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136541922</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43495</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>515222</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7010563</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136541922</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136544254</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43316</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>515172</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7010574</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136544254</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136544256</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43316</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>515091</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7010581</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136544256</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136544263</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43316</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>515130</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7010582</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136544263</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136545873</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514460</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7010741</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136545873</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136547490</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514706</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7010666</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547490</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136549634</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514466</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7010741</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136549634</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136543832</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>515150</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7010569</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136543832</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136540819</v>
+      </c>
+      <c r="B17" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>515486</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7010443</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136540819</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136549048</v>
+      </c>
+      <c r="B18" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>514892</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7010603</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136549048</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136544765</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110059</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>514712</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7010664</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136544765</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136547755</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98271</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>514730</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7010657</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547755</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136540277</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100955</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>515204</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7010568</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136540277</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136541904</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100955</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>514660</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7010685</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136541904</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136547730</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100955</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>515146</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7010572</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547730</t>
         </is>
       </c>
     </row>
@@ -926,6 +3054,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105365</v>
+        <v>105368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136543832</v>
       </c>
       <c r="B16" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136540819</v>
       </c>
       <c r="B17" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136549048</v>
       </c>
       <c r="B18" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136544765</v>
       </c>
       <c r="B19" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136547755</v>
       </c>
       <c r="B20" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136540277</v>
       </c>
       <c r="B21" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136541904</v>
       </c>
       <c r="B22" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136547730</v>
       </c>
       <c r="B23" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105368</v>
+        <v>105369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136543832</v>
       </c>
       <c r="B16" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136540819</v>
       </c>
       <c r="B17" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136549048</v>
       </c>
       <c r="B18" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136544765</v>
       </c>
       <c r="B19" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136547755</v>
       </c>
       <c r="B20" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136540277</v>
       </c>
       <c r="B21" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136541904</v>
       </c>
       <c r="B22" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136547730</v>
       </c>
       <c r="B23" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105369</v>
+        <v>105374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>136543593</v>
       </c>
       <c r="B5" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136547430</v>
       </c>
       <c r="B6" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136550510</v>
       </c>
       <c r="B7" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136541918</v>
       </c>
       <c r="B8" t="n">
-        <v>43495</v>
+        <v>43497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136541922</v>
       </c>
       <c r="B9" t="n">
-        <v>43495</v>
+        <v>43497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>136544254</v>
       </c>
       <c r="B10" t="n">
-        <v>43316</v>
+        <v>43318</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136544256</v>
       </c>
       <c r="B11" t="n">
-        <v>43316</v>
+        <v>43318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136544263</v>
       </c>
       <c r="B12" t="n">
-        <v>43316</v>
+        <v>43318</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136543832</v>
       </c>
       <c r="B16" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136540819</v>
       </c>
       <c r="B17" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136549048</v>
       </c>
       <c r="B18" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136544765</v>
       </c>
       <c r="B19" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136547755</v>
       </c>
       <c r="B20" t="n">
-        <v>98275</v>
+        <v>98280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136540277</v>
       </c>
       <c r="B21" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136541904</v>
       </c>
       <c r="B22" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136547730</v>
       </c>
       <c r="B23" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105374</v>
+        <v>105376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136543832</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136540819</v>
       </c>
       <c r="B17" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136549048</v>
       </c>
       <c r="B18" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136544765</v>
       </c>
       <c r="B19" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136547755</v>
       </c>
       <c r="B20" t="n">
-        <v>98280</v>
+        <v>98282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>136540277</v>
       </c>
       <c r="B21" t="n">
-        <v>100964</v>
+        <v>100966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136541904</v>
       </c>
       <c r="B22" t="n">
-        <v>100964</v>
+        <v>100966</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2949,7 +2949,7 @@
         <v>136547730</v>
       </c>
       <c r="B23" t="n">
-        <v>100964</v>
+        <v>100966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60271280</v>
+        <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105128</v>
+        <v>105376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,19 +841,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverede strand invid Indalsälven, Indalsälven, Stugun, Jmt</t>
+          <t>Magrinatorpet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -863,7 +860,7 @@
         <v>7010750</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,12 +884,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,24 +898,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60271280</t>
+          <t>https://artportalen.se/Sighting/136949656</t>
         </is>
       </c>
     </row>
@@ -2204,10 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136543832</v>
+        <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99355</v>
+        <v>99252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,34 +2217,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Z771 Stugun, Jmt</t>
+          <t>Magrinatorpet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515150</v>
+        <v>514463</v>
       </c>
       <c r="R16" t="n">
-        <v>7010569</v>
+        <v>7010735</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2269,12 +2279,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,18 +2293,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Signe Jönsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2304,16 +2315,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136543832</t>
+          <t>https://artportalen.se/Sighting/136950079</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136540819</v>
+        <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>108116</v>
+        <v>99355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2332,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219933</v>
+        <v>219811</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2356,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515486</v>
+        <v>515150</v>
       </c>
       <c r="R17" t="n">
-        <v>7010443</v>
+        <v>7010569</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,12 +2386,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2411,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2410,13 +2421,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136540819</t>
+          <t>https://artportalen.se/Sighting/136543832</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136549048</v>
+        <v>136540819</v>
       </c>
       <c r="B18" t="n">
         <v>108116</v>
@@ -2451,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514892</v>
+        <v>515486</v>
       </c>
       <c r="R18" t="n">
-        <v>7010603</v>
+        <v>7010443</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,38 +2527,38 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136549048</t>
+          <t>https://artportalen.se/Sighting/136540819</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136544765</v>
+        <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>110070</v>
+        <v>108116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220204</v>
+        <v>219933</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514712</v>
+        <v>514892</v>
       </c>
       <c r="R19" t="n">
-        <v>7010664</v>
+        <v>7010603</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2587,12 +2598,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2622,16 +2633,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136544765</t>
+          <t>https://artportalen.se/Sighting/136549048</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136547755</v>
+        <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>98282</v>
+        <v>110070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,21 +2650,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222112</v>
+        <v>220204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514730</v>
+        <v>514712</v>
       </c>
       <c r="R20" t="n">
-        <v>7010657</v>
+        <v>7010664</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2693,12 +2704,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,7 +2729,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2728,33 +2739,33 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136547755</t>
+          <t>https://artportalen.se/Sighting/136544765</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136540277</v>
+        <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>100966</v>
+        <v>110070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222584</v>
+        <v>220204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2762,17 +2773,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Z771 Stugun, Jmt</t>
+          <t>Magrinatorpet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515204</v>
+        <v>514468</v>
       </c>
       <c r="R21" t="n">
-        <v>7010568</v>
+        <v>7010739</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2799,12 +2818,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,18 +2832,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Signe Jönsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2834,38 +2854,38 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136540277</t>
+          <t>https://artportalen.se/Sighting/136950080</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136541904</v>
+        <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>100966</v>
+        <v>98282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222584</v>
+        <v>222112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514660</v>
+        <v>514730</v>
       </c>
       <c r="R22" t="n">
-        <v>7010685</v>
+        <v>7010657</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2940,13 +2960,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136541904</t>
+          <t>https://artportalen.se/Sighting/136547755</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136547730</v>
+        <v>136540277</v>
       </c>
       <c r="B23" t="n">
         <v>100966</v>
@@ -2981,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515146</v>
+        <v>515204</v>
       </c>
       <c r="R23" t="n">
-        <v>7010572</v>
+        <v>7010568</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3011,12 +3031,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,15 +3056,227 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136540277</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136541904</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100966</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514660</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7010685</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
           <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136541904</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136547730</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100966</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Z771 Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>515146</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7010572</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136547730</t>
         </is>
@@ -3074,6 +3306,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105376</v>
+        <v>105382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105376</v>
+        <v>105382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99252</v>
+        <v>99258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100966</v>
+        <v>100972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100966</v>
+        <v>100972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100966</v>
+        <v>100972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105382</v>
+        <v>105384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105382</v>
+        <v>105384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99258</v>
+        <v>99260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100972</v>
+        <v>100974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100972</v>
+        <v>100974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100972</v>
+        <v>100974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105384</v>
+        <v>105385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105384</v>
+        <v>105385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99260</v>
+        <v>99261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100974</v>
+        <v>100975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100974</v>
+        <v>100975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100974</v>
+        <v>100975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105385</v>
+        <v>105391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105385</v>
+        <v>105391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99261</v>
+        <v>99267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105391</v>
+        <v>105395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105391</v>
+        <v>105395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99267</v>
+        <v>99271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100981</v>
+        <v>100985</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100981</v>
+        <v>100985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100981</v>
+        <v>100985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105395</v>
+        <v>105397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105395</v>
+        <v>105397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100985</v>
+        <v>100987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100985</v>
+        <v>100987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100985</v>
+        <v>100987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105397</v>
+        <v>105399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105397</v>
+        <v>105399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99273</v>
+        <v>99275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105399</v>
+        <v>105412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105399</v>
+        <v>105412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136543593</v>
       </c>
       <c r="B5" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136547430</v>
       </c>
       <c r="B6" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136550510</v>
       </c>
       <c r="B7" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136541918</v>
       </c>
       <c r="B8" t="n">
-        <v>43497</v>
+        <v>43510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136541922</v>
       </c>
       <c r="B9" t="n">
-        <v>43497</v>
+        <v>43510</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136544254</v>
       </c>
       <c r="B10" t="n">
-        <v>43318</v>
+        <v>43331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136544256</v>
       </c>
       <c r="B11" t="n">
-        <v>43318</v>
+        <v>43331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136544263</v>
       </c>
       <c r="B12" t="n">
-        <v>43318</v>
+        <v>43331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99275</v>
+        <v>99288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>100989</v>
+        <v>101002</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>100989</v>
+        <v>101002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>100989</v>
+        <v>101002</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105412</v>
+        <v>105414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136545658</v>
       </c>
       <c r="B4" t="n">
-        <v>105412</v>
+        <v>105414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136543593</v>
       </c>
       <c r="B5" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136547430</v>
       </c>
       <c r="B6" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136550510</v>
       </c>
       <c r="B7" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136541918</v>
       </c>
       <c r="B8" t="n">
-        <v>43510</v>
+        <v>43512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136541922</v>
       </c>
       <c r="B9" t="n">
-        <v>43510</v>
+        <v>43512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136544254</v>
       </c>
       <c r="B10" t="n">
-        <v>43331</v>
+        <v>43333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136544256</v>
       </c>
       <c r="B11" t="n">
-        <v>43331</v>
+        <v>43333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136544263</v>
       </c>
       <c r="B12" t="n">
-        <v>43331</v>
+        <v>43333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>136545873</v>
       </c>
       <c r="B13" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136547490</v>
       </c>
       <c r="B14" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136549634</v>
       </c>
       <c r="B15" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99288</v>
+        <v>99290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136543832</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136540819</v>
       </c>
       <c r="B18" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136549048</v>
       </c>
       <c r="B19" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136544765</v>
       </c>
       <c r="B20" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>136547755</v>
       </c>
       <c r="B22" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>136540277</v>
       </c>
       <c r="B23" t="n">
-        <v>101002</v>
+        <v>101004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136541904</v>
       </c>
       <c r="B24" t="n">
-        <v>101002</v>
+        <v>101004</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>136547730</v>
       </c>
       <c r="B25" t="n">
-        <v>101002</v>
+        <v>101004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105414</v>
+        <v>105417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99290</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105417</v>
+        <v>105436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105436</v>
+        <v>105437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99304</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105437</v>
+        <v>105442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99304</v>
+        <v>99309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105442</v>
+        <v>105445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105445</v>
+        <v>105451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99311</v>
+        <v>99317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105451</v>
+        <v>105452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105452</v>
+        <v>105464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99317</v>
+        <v>99329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105464</v>
+        <v>105465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105465</v>
+        <v>105468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99330</v>
+        <v>99333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105468</v>
+        <v>105470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99333</v>
+        <v>99334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2123-2026 artfynd.xlsx
+++ b/artfynd/A 2123-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136949656</v>
       </c>
       <c r="B3" t="n">
-        <v>105470</v>
+        <v>105474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>136950079</v>
       </c>
       <c r="B16" t="n">
-        <v>99334</v>
+        <v>99337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136950080</v>
       </c>
       <c r="B21" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
